--- a/sample_data/TRD_backlog_2026-09.xlsx
+++ b/sample_data/TRD_backlog_2026-09.xlsx
@@ -471,12 +471,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COR-MDRR-NKJ</t>
+          <t>COR-KBH-KHTG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>COR-MDRR-NKJ-ohe_mast</t>
+          <t>COR-KBH-KHTG-ohe_mast</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3.35</v>
+        <v>2.29</v>
       </c>
       <c r="H2" t="n">
         <v>15</v>
@@ -509,17 +509,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COR-KAVM-WCN</t>
+          <t>COR-RNL-DDE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>COR-KAVM-WCN-ohe_mast</t>
+          <t>COR-RNL-DDE-ohe_mast</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>ohe_wire_wear</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -529,27 +529,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5.8</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COR-MLGH-SMPA</t>
+          <t>COR-LBA-MWP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>COR-MLGH-SMPA-ohe_mast</t>
+          <t>COR-LBA-MWP-ohe_mast</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -559,93 +559,87 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="H4" t="n">
-        <v>15</v>
+        <v>1.89</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-12 23:15</t>
+          <t>2026-09-14 23:15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-13 01:55</t>
+          <t>2026-09-15 01:08</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COR-NMA-GGH</t>
+          <t>COR-PLV-WTR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>COR-NMA-GGH-ohe_mast</t>
+          <t>COR-PLV-WTR-ohe_mast</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="H5" t="n">
-        <v>20</v>
+        <v>3.17</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-12 23:30</t>
+          <t>2026-09-14 23:30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-13 04:21</t>
+          <t>2026-09-15 02:40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COR-TVNL-KDMD</t>
+          <t>COR-SVZ-BKSA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COR-TVNL-KDMD-ohe_mast</t>
+          <t>COR-SVZ-BKSA-ohe_mast</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -655,7 +649,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -665,14 +659,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="H6" t="n">
-        <v>30</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="7">
@@ -707,370 +698,377 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5.54</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COR-JLR-CKE</t>
+          <t>COR-BSR-JCNR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>COR-JLR-CKE-ohe_mast</t>
+          <t>COR-BSR-JCNR-ohe_mast</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>ohe_wire_wear</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5.7</v>
+        <v>2.47</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-09-14 01:43</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COR-BTHL-BNR</t>
+          <t>COR-ISH-NOI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>COR-BTHL-BNR-ohe_mast</t>
+          <t>COR-ISH-NOI-ohe_mast</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="H9" t="n">
-        <v>30</v>
+        <v>3.62</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:07</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COR-SBNM-JJG</t>
+          <t>COR-UMED-SWF</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COR-SBNM-JJG-ohe_mast</t>
+          <t>COR-UMED-SWF-ohe_mast</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4.17</v>
+        <v>3.67</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-15 00:15</t>
+          <t>2026-09-14 23:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-15 04:25</t>
+          <t>2026-09-15 02:40</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COR-AKJ-CHBS</t>
+          <t>COR-GNJ-KNP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COR-AKJ-CHBS-ohe_mast</t>
+          <t>COR-GNJ-KNP-ohe_mast</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="H11" t="n">
-        <v>30</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COR-MVLK-KYJ</t>
+          <t>COR-MDPD-SRPM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COR-MVLK-KYJ-ohe_mast</t>
+          <t>COR-MDPD-SRPM-ohe_mast</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3.64</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COR-JDA-KHDP</t>
+          <t>COR-BLND-KUPR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>COR-JDA-KHDP-ohe_mast</t>
+          <t>COR-BLND-KUPR-ohe_mast</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>7.98</v>
+        <v>2.91</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COR-BLND-KUPR</t>
+          <t>COR-MGC-MUE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>COR-BLND-KUPR-ohe_mast</t>
+          <t>COR-MGC-MUE-ohe_mast</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>ohe_wire_wear</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="H14" t="n">
-        <v>20</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COR-DNPR-RTJ</t>
+          <t>COR-NRK-GDN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>COR-DNPR-RTJ-ohe_mast</t>
+          <t>COR-NRK-GDN-ohe_mast</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-09-15 11:30</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-09-15 17:26</t>
-        </is>
+        <v>4.11</v>
+      </c>
+      <c r="H15" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COR-KGP-GMDN</t>
+          <t>COR-DMA-BURN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COR-KGP-GMDN-ohe_mast</t>
+          <t>COR-DMA-BURN-ohe_mast</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>6.47</v>
-      </c>
-      <c r="H16" t="n">
-        <v>20</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>COR-BDPK-MRDL</t>
+          <t>COR-PRTP-MTC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COR-BDPK-MRDL-ohe_mast</t>
+          <t>COR-PRTP-MTC-ohe_mast</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>ohe_wire_wear</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1080,170 +1078,156 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2.44</v>
+        <v>1.9</v>
       </c>
       <c r="H17" t="n">
-        <v>20</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-09-13 02:15</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-09-13 04:41</t>
-        </is>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COR-DGD-GW</t>
+          <t>COR-DPU-NLN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COR-DGD-GW-ohe_mast</t>
+          <t>COR-DPU-NLN-ohe_mast</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-09-17 14:00</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-09-17 19:10</t>
-        </is>
+        <v>3.91</v>
+      </c>
+      <c r="H18" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>COR-ADI-SBI</t>
+          <t>COR-RNL-DDE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>COR-ADI-SBI-ohe_mast</t>
+          <t>COR-RNL-DDE-ohe_mast</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>6.1</v>
+        <v>4.08</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:34</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>COR-GRKN-JSRD</t>
+          <t>COR-MZU-PCV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>COR-GRKN-JSRD-ohe_mast</t>
+          <t>COR-MZU-PCV-ohe_mast</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-09-14 00:30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-09-14 06:54</t>
-        </is>
+        <v>1.83</v>
+      </c>
+      <c r="H20" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>COR-BXN-KEV</t>
+          <t>COR-SHIV-ALN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COR-BXN-KEV-ohe_mast</t>
+          <t>COR-SHIV-ALN-ohe_mast</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1253,30 +1237,40 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2.72</v>
+        <v>3.67</v>
       </c>
       <c r="H21" t="n">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-17 10:30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:10</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COR-BLM-GAJU</t>
+          <t>COR-BVI-DIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COR-BLM-GAJU-ohe_mast</t>
+          <t>COR-BVI-DIC-ohe_mast</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1286,72 +1280,95 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2.77</v>
+        <v>1.56</v>
+      </c>
+      <c r="H22" t="n">
+        <v>15</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-13 02:15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-09-13 03:48</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>COR-LKB-SVRP</t>
+          <t>COR-BISH-JOR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>COR-LKB-SVRP-ohe_mast</t>
+          <t>COR-BISH-JOR-ohe_mast</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>7.87</v>
+        <v>2.46</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-17 11:00</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:27</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>COR-BVI-DIC</t>
+          <t>COR-MGO-CNHL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>COR-BVI-DIC-ohe_mast</t>
+          <t>COR-MGO-CNHL-ohe_mast</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1361,45 +1378,45 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="H24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-12 02:15</t>
+          <t>2026-09-16 14:15</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-12 04:21</t>
+          <t>2026-09-16 16:44</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COR-BISH-JOR</t>
+          <t>COR-HLR-KPA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>COR-BISH-JOR-ohe_mast</t>
+          <t>COR-HLR-KPA-ohe_mast</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>ohe_wire_wear</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1409,125 +1426,115 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-09-16 11:00</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-09-16 14:39</t>
-        </is>
+        <v>3.18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>COR-MGO-CNHL</t>
+          <t>COR-DMA-BURN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COR-MGO-CNHL-ohe_mast</t>
+          <t>COR-DMA-BURN-ohe_mast</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>ohe_wire_wear</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H26" t="n">
-        <v>20</v>
+        <v>1.62</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-16 14:15</t>
+          <t>2026-09-19 01:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-16 17:57</t>
+          <t>2026-09-19 02:37</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>COR-DLO-BNV</t>
+          <t>COR-KBH-KHTG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COR-DLO-BNV-ohe_mast</t>
+          <t>COR-KBH-KHTG-ohe_mast</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>ohe_wire_wear</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3.16</v>
+        <v>3.87</v>
+      </c>
+      <c r="H27" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COR-RSA-MXA</t>
+          <t>COR-BNKI-HPI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>COR-RSA-MXA-ohe_mast</t>
+          <t>COR-BNKI-HPI-ohe_mast</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1537,37 +1544,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4.55</v>
+        <v>3.57</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-16 11:00</t>
+          <t>2026-09-16 10:30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-16 15:33</t>
+          <t>2026-09-16 14:04</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COR-ABD-GGM</t>
+          <t>COR-NRK-GDN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>COR-ABD-GGM-ohe_mast</t>
+          <t>COR-NRK-GDN-ohe_mast</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1577,37 +1584,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3.04</v>
+        <v>4.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-09-16 01:00</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-09-16 05:48</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COR-DIBL-HLB</t>
+          <t>COR-SVZ-BKSA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>COR-DIBL-HLB-ohe_mast</t>
+          <t>COR-SVZ-BKSA-ohe_mast</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1617,37 +1637,37 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>5.55</v>
+        <v>4.87</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-15 10:30</t>
+          <t>2026-09-13 10:30</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-15 16:03</t>
+          <t>2026-09-13 15:22</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COR-AII-DOZ</t>
+          <t>COR-KBH-KHTG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>COR-AII-DOZ-ohe_mast</t>
+          <t>COR-KBH-KHTG-ohe_mast</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1657,83 +1677,77 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="H31" t="n">
-        <v>15</v>
+        <v>3.21</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-18 01:00</t>
+          <t>2026-09-19 00:30</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-09-18 08:39</t>
+          <t>2026-09-19 03:42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>COR-PKD-DMM</t>
+          <t>COR-KDH-TGH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>COR-PKD-DMM-ohe_mast</t>
+          <t>COR-KDH-TGH-ohe_mast</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="H32" t="n">
-        <v>15</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>COR-JGDL-SNR</t>
+          <t>COR-KHTG-KBH</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>COR-JGDL-SNR-ohe_mast</t>
+          <t>COR-KHTG-KBH-ohe_mast</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1743,155 +1757,168 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>COR-QRP-GILL</t>
+          <t>COR-RGJI-DPRA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>COR-QRP-GILL-ohe_mast</t>
+          <t>COR-RGJI-DPRA-ohe_mast</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-09-12 01:00</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-09-12 03:10</t>
-        </is>
+        <v>1.83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>COR-SUW-BVB</t>
+          <t>COR-KBH-KHTG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>COR-SUW-BVB-ohe_mast</t>
+          <t>COR-KBH-KHTG-ohe_mast</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>ohe_wire_wear</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>4.9</v>
+        <v>3.42</v>
+      </c>
+      <c r="H35" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:30</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-09-16 03:55</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COR-JHW-DKRA</t>
+          <t>COR-DTF-GOS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>COR-JHW-DKRA-ohe_mast</t>
+          <t>COR-DTF-GOS-ohe_mast</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>5.15</v>
+        <v>4.15</v>
+      </c>
+      <c r="H36" t="n">
+        <v>15</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-09-13 15:24</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>COR-ASK-ADHL</t>
+          <t>COR-MQX-GHQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>COR-ASK-ADHL-ohe_mast</t>
+          <t>COR-MQX-GHQ-ohe_mast</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>ohe_wire_wear</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1901,32 +1928,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3.39</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>COR-BGAN-GADM</t>
+          <t>COR-EKH-SRY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>COR-BGAN-GADM-ohe_mast</t>
+          <t>COR-EKH-SRY-ohe_mast</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1936,153 +1963,150 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>5.29</v>
+        <v>4.87</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-09-18 00:30</t>
+          <t>2026-09-17 22:15</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-09-18 05:47</t>
+          <t>2026-09-18 03:07</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>COR-CGKR-CGKP</t>
+          <t>COR-KDH-TGH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>COR-CGKR-CGKP-ohe_mast</t>
+          <t>COR-KDH-TGH-ohe_mast</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="H39" t="n">
-        <v>15</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>COR-GGA-SBO</t>
+          <t>COR-GNJ-KNP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>COR-GGA-SBO-ohe_mast</t>
+          <t>COR-GNJ-KNP-ohe_mast</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>4.34</v>
+        <v>3.46</v>
+      </c>
+      <c r="H40" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>COR-AMB-LJR</t>
+          <t>COR-DHRY-HJI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>COR-AMB-LJR-ohe_mast</t>
+          <t>COR-DHRY-HJI-ohe_mast</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="H41" t="n">
-        <v>20</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>COR-NRDP-VLG</t>
+          <t>COR-KHTG-KBH</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>COR-NRDP-VLG-ohe_mast</t>
+          <t>COR-KHTG-KBH-ohe_mast</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2092,27 +2116,27 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>5.59</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>COR-OREH-CKH</t>
+          <t>COR-AMC-BTGH</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>COR-OREH-CKH-ohe_mast</t>
+          <t>COR-AMC-BTGH-ohe_mast</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2127,115 +2151,115 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3.86</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>COR-WL-KZJ</t>
+          <t>COR-TIS-GAG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>COR-WL-KZJ-ohe_mast</t>
+          <t>COR-TIS-GAG-ohe_mast</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="H44" t="n">
-        <v>30</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>COR-MAS-BBQ</t>
+          <t>COR-IDJ-KNP</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>COR-MAS-BBQ-ohe_mast</t>
+          <t>COR-IDJ-KNP-ohe_mast</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>7.9</v>
+        <v>2.4</v>
+      </c>
+      <c r="H45" t="n">
+        <v>30</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-09-17 02:15</t>
+          <t>2026-09-16 23:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-09-17 10:09</t>
+          <t>2026-09-17 01:24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>COR-KHA-SGBJ</t>
+          <t>COR-DMA-BURN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>COR-KHA-SGBJ-ohe_mast</t>
+          <t>COR-DMA-BURN-ohe_mast</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2245,62 +2269,72 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3.64</v>
+        <v>3.01</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:15</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-09-17 03:15</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>COR-GGJ-KTHE</t>
+          <t>COR-KLJI-CLKA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COR-GGJ-KTHE-ohe_mast</t>
+          <t>COR-KLJI-CLKA-ohe_mast</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>5.81</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>COR-BZA-SC</t>
+          <t>COR-KDHA-VRG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>COR-BZA-SC-ohe_mast</t>
+          <t>COR-KDHA-VRG-ohe_mast</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2310,42 +2344,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-09-18 00:15</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-09-18 07:37</t>
-        </is>
+        <v>2.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>COR-CHC-MSAE</t>
+          <t>COR-TVNL-KDMD</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>COR-CHC-MSAE-ohe_mast</t>
+          <t>COR-TVNL-KDMD-ohe_mast</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2355,95 +2379,82 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2.07</v>
+        <v>4.51</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-21 11:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-09-20 01:04</t>
+          <t>2026-09-21 15:30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>COR-SOU-TB</t>
+          <t>COR-GAG-KITA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>COR-SOU-TB-ohe_mast</t>
+          <t>COR-GAG-KITA-ohe_mast</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="H50" t="n">
-        <v>20</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-09-12 23:00</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-09-13 06:09</t>
-        </is>
+        <v>1.92</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>COR-GNNA-RPUR</t>
+          <t>COR-NBS-NCB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>COR-GNNA-RPUR-ohe_mast</t>
+          <t>COR-NBS-NCB-ohe_mast</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2453,125 +2464,135 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>4.69</v>
+        <v>1.94</v>
       </c>
       <c r="H51" t="n">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:15</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-09-13 13:11</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>COR-DG-EDU</t>
+          <t>COR-GNGD-KUU</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>COR-DG-EDU-ohe_mast</t>
+          <t>COR-GNGD-KUU-ohe_mast</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>7</v>
+        <v>3.01</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-09-17 14:15</t>
+          <t>2026-09-15 01:15</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-09-17 21:15</t>
+          <t>2026-09-15 04:15</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>COR-MYE-PGW</t>
+          <t>COR-KBH-KHTG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>COR-MYE-PGW-ohe_mast</t>
+          <t>COR-KBH-KHTG-ohe_mast</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>7.16</v>
+        <v>1.78</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-09-20 11:00</t>
+          <t>2026-09-19 22:15</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-09-20 18:09</t>
+          <t>2026-09-20 00:01</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>COR-TNLR-KRMG</t>
+          <t>COR-RPH-MLV</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>COR-TNLR-KRMG-ohe_mast</t>
+          <t>COR-RPH-MLV-ohe_mast</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>ohe_wire_wear</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2581,75 +2602,72 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>6.04</v>
+        <v>4.42</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-09-20 02:15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-09-20 06:40</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>COR-KXB-MNV</t>
+          <t>COR-KDHA-VRG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>COR-KXB-MNV-ohe_mast</t>
+          <t>COR-KDHA-VRG-ohe_mast</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="H55" t="n">
-        <v>30</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2026-09-12 23:30</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2026-09-13 02:03</t>
-        </is>
+        <v>2.23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>COR-KWP-KUT</t>
+          <t>COR-BCQ-STN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>COR-KWP-KUT-ohe_mast</t>
+          <t>COR-BCQ-STN-ohe_mast</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2664,75 +2682,72 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2026-09-14 22:15</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>2026-09-15 03:18</t>
-        </is>
+        <v>4.95</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>COR-TDP-BEG</t>
+          <t>COR-GKD-BDHA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>COR-TDP-BEG-ohe_mast</t>
+          <t>COR-GKD-BDHA-ohe_mast</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="H57" t="n">
-        <v>20</v>
+        <v>4.88</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:15</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-09-16 03:07</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>COR-DAD-BYD</t>
+          <t>COR-SBI-SBT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>COR-DAD-BYD-ohe_mast</t>
+          <t>COR-SBI-SBT-ohe_mast</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2742,197 +2757,196 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2026-09-15 23:30</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>2026-09-16 04:28</t>
-        </is>
+        <v>3.61</v>
+      </c>
+      <c r="H58" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>COR-MQN-MHBT</t>
+          <t>COR-DOR-MNKB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>COR-MQN-MHBT-ohe_mast</t>
+          <t>COR-DOR-MNKB-ohe_mast</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
+      </c>
+      <c r="H59" t="n">
+        <v>20</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:15</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-09-14 02:55</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>COR-PHN-MLS</t>
+          <t>COR-RES-SGJ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>COR-PHN-MLS-ohe_mast</t>
+          <t>COR-RES-SGJ-ohe_mast</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2026-09-12 22:00</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>2026-09-13 02:01</t>
-        </is>
+        <v>4.52</v>
+      </c>
+      <c r="H60" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>COR-BCQ-STN</t>
+          <t>COR-VM-MYP</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>COR-BCQ-STN-ohe_mast</t>
+          <t>COR-VM-MYP-ohe_mast</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>7.91</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>COR-CD-BUPH</t>
+          <t>COR-NRK-GDN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>COR-CD-BUPH-ohe_mast</t>
+          <t>COR-NRK-GDN-ohe_mast</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>3.37</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>COR-KOAA-PTKR</t>
+          <t>COR-MSK-MNE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>COR-KOAA-PTKR-ohe_mast</t>
+          <t>COR-MSK-MNE-ohe_mast</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2942,27 +2956,37 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>6.68</v>
+        <v>3.66</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:30</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:09</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>COR-ROZA-KH</t>
+          <t>COR-SHIV-ALN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>COR-ROZA-KH-ohe_mast</t>
+          <t>COR-SHIV-ALN-ohe_mast</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2986,107 +3010,91 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>5.62</v>
+        <v>2.99</v>
       </c>
       <c r="H64" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>COR-DOR-MNKB</t>
+          <t>COR-NBS-NCB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>COR-DOR-MNKB-ohe_mast</t>
+          <t>COR-NBS-NCB-ohe_mast</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="H65" t="n">
-        <v>20</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2026-09-12 23:15</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>2026-09-13 04:59</t>
-        </is>
+        <v>2.93</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>COR-RES-SGJ</t>
+          <t>COR-ISH-NOI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>COR-RES-SGJ-ohe_mast</t>
+          <t>COR-ISH-NOI-ohe_mast</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="H66" t="n">
-        <v>20</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>COR-FRH-MLW</t>
+          <t>COR-JU-BGKT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>COR-FRH-MLW-ohe_mast</t>
+          <t>COR-JU-BGKT-ohe_mast</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3101,32 +3109,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>3.47</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>COR-KODR-GTWD</t>
+          <t>COR-CUE-TISI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>COR-KODR-GTWD-ohe_mast</t>
+          <t>COR-CUE-TISI-ohe_mast</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3136,27 +3144,27 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>3.02</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>COR-KLA-MWUE</t>
+          <t>COR-DCK-HLB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>COR-KLA-MWUE-ohe_mast</t>
+          <t>COR-DCK-HLB-ohe_mast</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3176,22 +3184,22 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>COR-ABFC-NJP</t>
+          <t>COR-SVZ-BKSA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>COR-ABFC-NJP-ohe_mast</t>
+          <t>COR-SVZ-BKSA-ohe_mast</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3201,50 +3209,47 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="H70" t="n">
-        <v>30</v>
+        <v>4.43</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-09-12 00:15</t>
+          <t>2026-09-15 14:15</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-09-12 02:19</t>
+          <t>2026-09-15 18:40</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>COR-MYD-HTL</t>
+          <t>COR-KDH-TGH</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>COR-MYD-HTL-ohe_mast</t>
+          <t>COR-KDH-TGH-ohe_mast</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3254,65 +3259,62 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>7.4</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>COR-BRJN-BPH</t>
+          <t>COR-PVU-MYY</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>COR-BRJN-BPH-ohe_mast</t>
+          <t>COR-PVU-MYY-ohe_mast</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="H72" t="n">
-        <v>20</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>COR-FUT-DNWH</t>
+          <t>COR-PRKH-PCH</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>COR-FUT-DNWH-ohe_mast</t>
+          <t>COR-PRKH-PCH-ohe_mast</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3327,82 +3329,82 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>4.49</v>
+        <v>3.11</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:30</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2026-09-16 13:36</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>COR-MPG-KCO</t>
+          <t>COR-SBI-SBT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>COR-MPG-KCO-ohe_mast</t>
+          <t>COR-SBI-SBT-ohe_mast</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2026-09-20 14:30</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>2026-09-20 17:15</t>
-        </is>
+        <v>3.73</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>COR-BSX-FKB</t>
+          <t>COR-CTL-LDU</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>COR-BSX-FKB-ohe_mast</t>
+          <t>COR-CTL-LDU-ohe_mast</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3412,27 +3414,27 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>7.14</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>COR-DCK-HLB</t>
+          <t>COR-RHW-KUP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>COR-DCK-HLB-ohe_mast</t>
+          <t>COR-RHW-KUP-ohe_mast</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3442,27 +3444,37 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2.01</v>
+        <v>5</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-09-17 02:15</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2026-09-17 07:15</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>COR-ADR-BHT</t>
+          <t>COR-LMP-OEL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>COR-ADR-BHT-ohe_mast</t>
+          <t>COR-LMP-OEL-ohe_mast</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3472,32 +3484,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>4.21</v>
+        <v>2.67</v>
+      </c>
+      <c r="H77" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>COR-PDR-YEAM</t>
+          <t>COR-KHDI-PDH</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>COR-PDR-YEAM-ohe_mast</t>
+          <t>COR-KHDI-PDH-ohe_mast</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3512,80 +3527,67 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2026-09-12 11:30</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>2026-09-12 17:37</t>
-        </is>
+        <v>2.11</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>COR-AZ-DHPD</t>
+          <t>COR-DHRY-HJI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>COR-AZ-DHPD-ohe_mast</t>
+          <t>COR-DHRY-HJI-ohe_mast</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H79" t="n">
-        <v>20</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>COR-HND-MHDB</t>
+          <t>COR-BRLF-LMG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>COR-HND-MHDB-ohe_mast</t>
+          <t>COR-BRLF-LMG-ohe_mast</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3595,32 +3597,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>7.88</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>COR-MSD-SNRD</t>
+          <t>COR-CMA-JTTN</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>COR-MSD-SNRD-ohe_mast</t>
+          <t>COR-CMA-JTTN-ohe_mast</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3630,67 +3632,87 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>5.8</v>
+        <v>4.73</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-09-17 01:30</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2026-09-17 06:13</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>COR-HRNR-CKDL</t>
+          <t>COR-SFY-CAZ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>COR-HRNR-CKDL-ohe_mast</t>
+          <t>COR-SFY-CAZ-ohe_mast</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>traction_transformer_fault</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>5.54</v>
+        <v>1.59</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:15</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:50</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>COR-CTL-LDU</t>
+          <t>COR-CNC-RBG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>COR-CTL-LDU-ohe_mast</t>
+          <t>COR-CNC-RBG-ohe_mast</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>ohe_wire_wear</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3700,32 +3722,42 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>3</v>
+        <v>3.93</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-09-16 23:15</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2026-09-17 03:10</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>COR-SJF-DGJ</t>
+          <t>COR-ISH-NOI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>COR-SJF-DGJ-ohe_mast</t>
+          <t>COR-ISH-NOI-ohe_mast</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3735,85 +3767,82 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>8</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2026-09-16 02:15</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>2026-09-16 10:15</t>
-        </is>
+        <v>4.24</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>COR-LMP-OEL</t>
+          <t>COR-USD-DSD</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>COR-LMP-OEL-ohe_mast</t>
+          <t>COR-USD-DSD-ohe_mast</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="H85" t="n">
-        <v>30</v>
+        <v>4.65</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-09-22 02:30</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2026-09-22 07:09</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>COR-GUS-JUL</t>
+          <t>COR-SFK-BUDM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>COR-GUS-JUL-ohe_mast</t>
+          <t>COR-SFK-BUDM-ohe_mast</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>ohe_wire_wear</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3823,62 +3852,85 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>3.05</v>
+        <v>4.11</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-09-13 01:00</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2026-09-13 05:06</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>COR-JGZ-NIR</t>
+          <t>COR-CRR-KUE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>COR-JGZ-NIR-ohe_mast</t>
+          <t>COR-CRR-KUE-ohe_mast</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>ohe_wire_wear</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>7.88</v>
+        <v>3.58</v>
+      </c>
+      <c r="H87" t="n">
+        <v>20</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-09-19 14:00</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2026-09-19 17:34</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>COR-SOJN-SGD</t>
+          <t>COR-KHTG-KBH</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>COR-SOJN-SGD-ohe_mast</t>
+          <t>COR-KHTG-KBH-ohe_mast</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3888,77 +3940,77 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>5.65</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>COR-VKN-CEM</t>
+          <t>COR-KHTG-KBH</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>COR-VKN-CEM-ohe_mast</t>
+          <t>COR-KHTG-KBH-ohe_mast</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>7.13</v>
+        <v>1.94</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-09-17 00:30</t>
+          <t>2026-09-15 23:15</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-09-17 07:37</t>
+          <t>2026-09-16 01:11</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>COR-AYB-MNL</t>
+          <t>COR-MJGP-KMZ</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>COR-AYB-MNL-ohe_mast</t>
+          <t>COR-MJGP-KMZ-ohe_mast</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3968,117 +4020,110 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>6.32</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>COR-SFY-CAZ</t>
+          <t>COR-NBS-NCB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>COR-SFY-CAZ-ohe_mast</t>
+          <t>COR-NBS-NCB-ohe_mast</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>ohe_wire_wear</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>2026-09-18 00:15</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>2026-09-18 02:24</t>
-        </is>
+        <v>1.68</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>COR-ARNH-HPA</t>
+          <t>COR-GAG-KITA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>COR-ARNH-HPA-ohe_mast</t>
+          <t>COR-GAG-KITA-ohe_mast</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>ohe_wire_wear</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>5.45</v>
+        <v>4.66</v>
+      </c>
+      <c r="H92" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>COR-VM-KDMD</t>
+          <t>COR-SXT-SAMT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>COR-VM-KDMD-ohe_mast</t>
+          <t>COR-SXT-SAMT-ohe_mast</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4088,62 +4133,72 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>3.06</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>COR-TPPI-NLDA</t>
+          <t>COR-BRPK-NBE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>COR-TPPI-NLDA-ohe_mast</t>
+          <t>COR-BRPK-NBE-ohe_mast</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>2.04</v>
+        <v>2.65</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:00</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2026-09-20 02:39</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>COR-JNU-ZBD</t>
+          <t>COR-MTN-SIN</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>COR-JNU-ZBD-ohe_mast</t>
+          <t>COR-MTN-SIN-ohe_mast</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ohe_wire_wear</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4153,37 +4208,47 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>5.65</v>
+        <v>1.7</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-09-14 02:15</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2026-09-14 03:57</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>COR-AMY-KVU</t>
+          <t>COR-BP-PTF</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>COR-AMY-KVU-ohe_mast</t>
+          <t>COR-BP-PTF-ohe_mast</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4193,27 +4258,30 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>2.61</v>
+        <v>4.42</v>
+      </c>
+      <c r="H96" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>COR-SOH-KVJ</t>
+          <t>COR-USD-DSD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>COR-SOH-KVJ-ohe_mast</t>
+          <t>COR-USD-DSD-ohe_mast</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4228,60 +4296,67 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>2.06</v>
+        <v>2.52</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:15</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2026-09-22 16:46</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>COR-JONR-NIR</t>
+          <t>COR-KHTG-KBH</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>COR-JONR-NIR-ohe_mast</t>
+          <t>COR-KHTG-KBH-ohe_mast</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>traction_transformer_fault</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="H98" t="n">
-        <v>15</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>COR-SUP-MVW</t>
+          <t>COR-BRLF-LMG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>COR-SUP-MVW-ohe_mast</t>
+          <t>COR-BRLF-LMG-ohe_mast</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4291,7 +4366,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4301,72 +4376,65 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2026-09-12 00:00</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>2026-09-12 03:00</t>
-        </is>
+        <v>3.25</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>COR-OML-MCRD</t>
+          <t>COR-KVA-UTL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>COR-OML-MCRD-ohe_mast</t>
+          <t>COR-KVA-UTL-ohe_mast</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>insulator_flashover_risk</t>
+          <t>feeder_fault</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>7.99</v>
+        <v>3.35</v>
+      </c>
+      <c r="H100" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>COR-RJGR-CTC</t>
+          <t>COR-BSR-JCNR</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>COR-RJGR-CTC-ohe_mast</t>
+          <t>COR-BSR-JCNR-ohe_mast</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>feeder_fault</t>
+          <t>insulator_flashover_risk</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4376,16 +4444,16 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>6.15</v>
+        <v>3.68</v>
       </c>
     </row>
   </sheetData>
